--- a/reports/20260507/Sprint_217_Zwayam.xlsx
+++ b/reports/20260507/Sprint_217_Zwayam.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,12 +36,8 @@
       <b val="1"/>
       <color rgb="00006100"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="009C0006"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -58,12 +54,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
         <bgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -85,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -94,9 +84,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -652,7 +639,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Status Code: 403 - Forbidden and all assertions should pass.</t>
+          <t>Status Code: 200 - OK and all assertions should pass.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,17 +647,15 @@
           <t>All assertions pass.</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Response Code: 403 - Forbidden
-Errors: Unexpected token '&lt;' at 1:1
-&lt;html&gt;
-^</t>
+          <t>Response Code: 200 - OK
+Assertions: *** *** C A N D I D A T E - C R E A T E D ***  ===&gt;  1607443 (PASS), *** *** A P P L I C A T E - C R E A T E D ***  ===&gt;  1440641 (PASS), *** I N T E R V I E W - I D ***  ==&gt;  65793 (PASS), *** I N T E R V I E W - L I N K ***  ==&gt;   (PASS), *** C A N D I D A T E - L I N K ***  ==&gt;   (PASS)</t>
         </is>
       </c>
     </row>
@@ -719,7 +704,7 @@
       <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Response Code: 200 - OK
-Assertions: *** I N T E R V I E W - F A I L E D - D E T A I L S ***  ==&gt;  Invalid input.  not found. (PASS)</t>
+Assertions: *** I N T E R V I E W - D E T A I L S ***  ==&gt;   (PASS)</t>
         </is>
       </c>
     </row>
@@ -768,7 +753,7 @@
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Response Code: 200 - OK
-Assertions: *** M A R K - I N T E R V I E W - F A I L E D ***  ==&gt;  Invalid input.  not found. (PASS)</t>
+Assertions: *** M A R K - I N T E R V I E W - C O M P L E T E D ***  ==&gt;  true (PASS)</t>
         </is>
       </c>
     </row>
@@ -817,7 +802,7 @@
       <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Response Code: 200 - OK
-Assertions: *** C A N C E L L E D - I N T E R V I E W  - F A I L E D ***  ==&gt;  Invalid input.  not found. (PASS)</t>
+Assertions: *** C A N C E L L E D - I N T E R V I E W - I D ***  ==&gt;  true (PASS)</t>
         </is>
       </c>
     </row>
